--- a/chongli_care_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/chongli_care_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度养护明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +35,14 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,13 +72,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5467,8 +5487,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>2025-12-28</t>
@@ -5679,8 +5697,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-01-30</t>
@@ -5759,8 +5775,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-02-05</t>
@@ -5795,8 +5809,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-02-10</t>
@@ -6139,8 +6151,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-03-23</t>
@@ -6175,8 +6185,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>2025-12-04</t>
@@ -6402,8 +6410,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>支付</t>
@@ -6474,8 +6480,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>支付</t>
@@ -6706,8 +6710,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>支付</t>
@@ -6778,8 +6780,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>支付</t>
@@ -6810,8 +6810,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>支付</t>
@@ -7122,8 +7120,6 @@
           <t>储值支付</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>支付</t>
@@ -7146,4 +7142,7557 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BX32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="30" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="21" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="30" customWidth="1" min="50" max="50"/>
+    <col width="6" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="15" customWidth="1" min="53" max="53"/>
+    <col width="7" customWidth="1" min="54" max="54"/>
+    <col width="6" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="56" max="56"/>
+    <col width="6" customWidth="1" min="57" max="57"/>
+    <col width="6" customWidth="1" min="58" max="58"/>
+    <col width="6" customWidth="1" min="59" max="59"/>
+    <col width="6" customWidth="1" min="60" max="60"/>
+    <col width="6" customWidth="1" min="61" max="61"/>
+    <col width="6" customWidth="1" min="62" max="62"/>
+    <col width="6" customWidth="1" min="63" max="63"/>
+    <col width="8" customWidth="1" min="64" max="64"/>
+    <col width="8" customWidth="1" min="65" max="65"/>
+    <col width="6" customWidth="1" min="66" max="66"/>
+    <col width="6" customWidth="1" min="67" max="67"/>
+    <col width="21" customWidth="1" min="68" max="68"/>
+    <col width="36" customWidth="1" min="69" max="69"/>
+    <col width="15" customWidth="1" min="70" max="70"/>
+    <col width="15" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="15" customWidth="1" min="73" max="73"/>
+    <col width="15" customWidth="1" min="74" max="74"/>
+    <col width="15" customWidth="1" min="75" max="75"/>
+    <col width="15" customWidth="1" min="76" max="76"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>业务</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>财年</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>营/非</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>财年序号</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>运营日序号</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>日序号</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>创建日期</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>支付次数</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>支付合计</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>退款次数</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>退款合计</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>订单结余</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>最后退款日期</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>最后退款时间</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>【支付1】日期</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>【支付1】时间</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>【支付1】金额</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>【支付1】支付方式</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>【支付1】支付账号</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>养护件数</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>维修费合计</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>普通养护费合计</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>减免合计</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>卡券减免合计</t>
+        </is>
+      </c>
+      <c r="AB1" s="4" t="inlineStr">
+        <is>
+          <t>养护直减合计</t>
+        </is>
+      </c>
+      <c r="AC1" s="4" t="inlineStr">
+        <is>
+          <t>服务项目</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>隐藏订单</t>
+        </is>
+      </c>
+      <c r="AE1" s="4" t="inlineStr">
+        <is>
+          <t>应分账金额</t>
+        </is>
+      </c>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>实分账金额</t>
+        </is>
+      </c>
+      <c r="AG1" s="4" t="inlineStr">
+        <is>
+          <t>待分账金额</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>业务</t>
+        </is>
+      </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="AL1" s="4" t="inlineStr">
+        <is>
+          <t>顾客openid</t>
+        </is>
+      </c>
+      <c r="AM1" s="4" t="inlineStr">
+        <is>
+          <t>收款方式</t>
+        </is>
+      </c>
+      <c r="AN1" s="4" t="inlineStr">
+        <is>
+          <t>支付账号</t>
+        </is>
+      </c>
+      <c r="AO1" s="4" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="AP1" s="4" t="inlineStr">
+        <is>
+          <t>业务日期</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>业务时间</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>结算日期</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
+          <t>结算时间</t>
+        </is>
+      </c>
+      <c r="AT1" s="4" t="inlineStr">
+        <is>
+          <t>支付总金额</t>
+        </is>
+      </c>
+      <c r="AU1" s="4" t="inlineStr">
+        <is>
+          <t>退款总金额</t>
+        </is>
+      </c>
+      <c r="AV1" s="4" t="inlineStr">
+        <is>
+          <t>订单结余</t>
+        </is>
+      </c>
+      <c r="AW1" s="4" t="inlineStr">
+        <is>
+          <t>店员姓名</t>
+        </is>
+      </c>
+      <c r="AX1" s="4" t="inlineStr">
+        <is>
+          <t>店员openid</t>
+        </is>
+      </c>
+      <c r="AY1" s="4" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="AZ1" s="4" t="inlineStr">
+        <is>
+          <t>临时订单</t>
+        </is>
+      </c>
+      <c r="BA1" s="4" t="inlineStr">
+        <is>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="BB1" s="4" t="inlineStr">
+        <is>
+          <t>正/闭</t>
+        </is>
+      </c>
+      <c r="BC1" s="4" t="inlineStr">
+        <is>
+          <t>装备</t>
+        </is>
+      </c>
+      <c r="BD1" s="4" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="BE1" s="4" t="inlineStr">
+        <is>
+          <t>型号</t>
+        </is>
+      </c>
+      <c r="BF1" s="4" t="inlineStr">
+        <is>
+          <t>尺码</t>
+        </is>
+      </c>
+      <c r="BG1" s="4" t="inlineStr">
+        <is>
+          <t>加急</t>
+        </is>
+      </c>
+      <c r="BH1" s="4" t="inlineStr">
+        <is>
+          <t>修刃</t>
+        </is>
+      </c>
+      <c r="BI1" s="4" t="inlineStr">
+        <is>
+          <t>打蜡</t>
+        </is>
+      </c>
+      <c r="BJ1" s="4" t="inlineStr">
+        <is>
+          <t>刮蜡</t>
+        </is>
+      </c>
+      <c r="BK1" s="4" t="inlineStr">
+        <is>
+          <t>维修</t>
+        </is>
+      </c>
+      <c r="BL1" s="4" t="inlineStr">
+        <is>
+          <t>维修费</t>
+        </is>
+      </c>
+      <c r="BM1" s="4" t="inlineStr">
+        <is>
+          <t>养护费</t>
+        </is>
+      </c>
+      <c r="BN1" s="4" t="inlineStr">
+        <is>
+          <t>直减</t>
+        </is>
+      </c>
+      <c r="BO1" s="4" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="BP1" s="4" t="inlineStr">
+        <is>
+          <t>取板日期</t>
+        </is>
+      </c>
+      <c r="BQ1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="BR1" s="4" t="inlineStr">
+        <is>
+          <t>安全检查人</t>
+        </is>
+      </c>
+      <c r="BS1" s="4" t="inlineStr">
+        <is>
+          <t>修刃人</t>
+        </is>
+      </c>
+      <c r="BT1" s="4" t="inlineStr">
+        <is>
+          <t>机打蜡人</t>
+        </is>
+      </c>
+      <c r="BU1" s="4" t="inlineStr">
+        <is>
+          <t>热打蜡人</t>
+        </is>
+      </c>
+      <c r="BV1" s="4" t="inlineStr">
+        <is>
+          <t>刮蜡人</t>
+        </is>
+      </c>
+      <c r="BW1" s="4" t="inlineStr">
+        <is>
+          <t>维修人</t>
+        </is>
+      </c>
+      <c r="BX1" s="4" t="inlineStr">
+        <is>
+          <t>发板人</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>45952</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10:26:11</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>45952</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>10:28:34</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1636371865</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>18601197897</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>1636371865</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>QJ_YH_251022_00001</t>
+        </is>
+      </c>
+      <c r="AP2" s="5" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>10:26:11</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>45952</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>18:00:02</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>18601197897</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>QJ_YH_251022_00010</t>
+        </is>
+      </c>
+      <c r="AP3" s="5" t="n">
+        <v>45952</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>18:00:02</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>45953</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20:06:47</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>18601197897</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>QJ_YH_251023_00001</t>
+        </is>
+      </c>
+      <c r="AP4" s="5" t="n">
+        <v>45953</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>20:06:47</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>45995</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17:13:10</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>45995</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>17:13:24</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>打蜡</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>15106929049</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>oHdTn5YIWYbgnxX9eFw-7_4obbIQ</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>WF_YH_251204_00027</t>
+        </is>
+      </c>
+      <c r="AP5" s="5" t="n">
+        <v>45995</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>17:13:10</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>RS/null</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN5" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP5" s="5" t="n">
+        <v>45996</v>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>储值</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>45997</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14:28:25</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>修刃</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>18601197897</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>QJ_YH_251206_00001</t>
+        </is>
+      </c>
+      <c r="AP6" s="5" t="n">
+        <v>45997</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>14:28:25</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>ABBA/ABBA</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP6" s="5" t="n">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>68</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19:11:48</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>19:12:39</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1615235183</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>13821559175</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>oHdTn5ZnUR7F2Iva9cCKi8GdHXAw</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>1615235183</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>WF_YH_251227_00076</t>
+        </is>
+      </c>
+      <c r="AP7" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>19:11:48</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN7" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP7" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>旗舰店打蜡</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>08:37:16</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>08:37:19</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡·维修</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>15106929049</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>oHdTn5YIWYbgnxX9eFw-7_4obbIQ</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>QJ_YH_251228_00001</t>
+        </is>
+      </c>
+      <c r="AP8" s="5" t="n">
+        <v>46019</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>08:37:16</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>朱</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Atomic/阿托米克</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP8" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>73</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16:44:52</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>16:45:12</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1615235183</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>蔡</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>15632382618</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>oHdTn5dlOTlM6NXNwmYlL4GG-kEA</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>1615235183</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>WF_YH_260101_00035</t>
+        </is>
+      </c>
+      <c r="AP9" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>16:44:52</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>蔡</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="BN9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP9" s="5" t="n">
+        <v>46024</v>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>79</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>46029</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17:09:03</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>46029</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>17:09:23</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>隋</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>15620997977</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>oHdTn5UmSXvlMH7P6__c9y4uitB8</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>QJ_YH_260107_00001</t>
+        </is>
+      </c>
+      <c r="AP10" s="5" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>17:09:03</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>隋</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>新增品牌</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP10" s="5" t="n">
+        <v>46030</v>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>武士团打蜡80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>23:34:37</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>23:34:59</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="6" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="n"/>
+      <c r="AE11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI11" s="6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ11" s="6" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+      <c r="AK11" s="6" t="inlineStr">
+        <is>
+          <t>13001240066</t>
+        </is>
+      </c>
+      <c r="AL11" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5VlFOq1fTF3Do-6dpdouwa8</t>
+        </is>
+      </c>
+      <c r="AM11" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO11" s="6" t="inlineStr">
+        <is>
+          <t>QJ_YH_260120_00001</t>
+        </is>
+      </c>
+      <c r="AP11" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="AQ11" s="6" t="inlineStr">
+        <is>
+          <t>23:34:37</t>
+        </is>
+      </c>
+      <c r="AR11" s="6" t="n"/>
+      <c r="AS11" s="6" t="n"/>
+      <c r="AT11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW11" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX11" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="AY11" s="6" t="n"/>
+      <c r="AZ11" s="6" t="n"/>
+      <c r="BA11" s="6" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+      <c r="BB11" s="6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC11" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD11" s="6" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="BE11" s="6" t="n"/>
+      <c r="BF11" s="6" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="BG11" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH11" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI11" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ11" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK11" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP11" s="7" t="n">
+        <v>46043</v>
+      </c>
+      <c r="BQ11" s="6" t="n"/>
+      <c r="BR11" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BS11" s="6" t="n"/>
+      <c r="BT11" s="6" t="n"/>
+      <c r="BU11" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BV11" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BW11" s="6" t="n"/>
+      <c r="BX11" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
+      <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="6" t="n"/>
+      <c r="AC12" s="6" t="n"/>
+      <c r="AD12" s="6" t="n"/>
+      <c r="AE12" s="6" t="n"/>
+      <c r="AF12" s="6" t="n"/>
+      <c r="AG12" s="6" t="n"/>
+      <c r="AH12" s="6" t="n"/>
+      <c r="AI12" s="6" t="n"/>
+      <c r="AJ12" s="6" t="n"/>
+      <c r="AK12" s="6" t="n"/>
+      <c r="AL12" s="6" t="n"/>
+      <c r="AM12" s="6" t="n"/>
+      <c r="AN12" s="6" t="n"/>
+      <c r="AO12" s="6" t="n"/>
+      <c r="AP12" s="6" t="n"/>
+      <c r="AQ12" s="6" t="n"/>
+      <c r="AR12" s="6" t="n"/>
+      <c r="AS12" s="6" t="n"/>
+      <c r="AT12" s="6" t="n"/>
+      <c r="AU12" s="6" t="n"/>
+      <c r="AV12" s="6" t="n"/>
+      <c r="AW12" s="6" t="n"/>
+      <c r="AX12" s="6" t="n"/>
+      <c r="AY12" s="6" t="n"/>
+      <c r="AZ12" s="6" t="n"/>
+      <c r="BA12" s="6" t="n"/>
+      <c r="BB12" s="6" t="n"/>
+      <c r="BC12" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD12" s="6" t="inlineStr">
+        <is>
+          <t>Burton</t>
+        </is>
+      </c>
+      <c r="BE12" s="6" t="n"/>
+      <c r="BF12" s="6" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="BG12" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH12" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI12" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ12" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK12" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP12" s="7" t="n">
+        <v>46043</v>
+      </c>
+      <c r="BQ12" s="6" t="n"/>
+      <c r="BR12" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BS12" s="6" t="n"/>
+      <c r="BT12" s="6" t="n"/>
+      <c r="BU12" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BV12" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BW12" s="6" t="n"/>
+      <c r="BX12" s="6" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17:57:27</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>17:57:51</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>冯</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>17645127089</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>oHdTn5RHuLE9t9ymxKBTU5AkJwAA</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>QJ_YH_260128_00001</t>
+        </is>
+      </c>
+      <c r="AP13" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>17:57:27</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>冯</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>新增品牌</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP13" s="5" t="n">
+        <v>46051</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>22:14:17</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>22:14:41</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>修刃</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>党</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>13910103049</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>oHdTn5armm18OqEyKNUFhbOYC50s</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>QJ_YH_260128_00002</t>
+        </is>
+      </c>
+      <c r="AP14" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>22:14:17</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>党</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Stockli/斯托克林</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP14" s="5" t="n">
+        <v>46051</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>46052</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>21:24:15</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>46052</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>21:24:20</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡·维修</t>
+        </is>
+      </c>
+      <c r="AE15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>13581876917</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>oHdTn5VnExE7HtR9KfYskSLZeXnk</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>QJ_YH_260130_00001</t>
+        </is>
+      </c>
+      <c r="AP15" s="5" t="n">
+        <v>46052</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>21:24:15</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>oHdTn5RBMZkgDb8KDc09Mbmm-j58</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>刘</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Fischer/费舍尔</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BM15" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP15" s="5" t="n">
+        <v>46053</v>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>储值消费</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>46053</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>13:54:57</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="7" t="n">
+        <v>46053</v>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>13:55:18</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="n"/>
+      <c r="AE16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI16" s="6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ16" s="6" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="AK16" s="6" t="inlineStr">
+        <is>
+          <t>17807641635</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5ZkojAWeTmv1jf0t9RvfTzg</t>
+        </is>
+      </c>
+      <c r="AM16" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN16" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO16" s="6" t="inlineStr">
+        <is>
+          <t>QJ_YH_260131_00001</t>
+        </is>
+      </c>
+      <c r="AP16" s="7" t="n">
+        <v>46053</v>
+      </c>
+      <c r="AQ16" s="6" t="inlineStr">
+        <is>
+          <t>13:54:57</t>
+        </is>
+      </c>
+      <c r="AR16" s="6" t="n"/>
+      <c r="AS16" s="6" t="n"/>
+      <c r="AT16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AU16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>段春敏</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5Yg9Z-02nOZ2mkavCWAVh8s</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="n"/>
+      <c r="AZ16" s="6" t="n"/>
+      <c r="BA16" s="6" t="inlineStr">
+        <is>
+          <t>秋</t>
+        </is>
+      </c>
+      <c r="BB16" s="6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC16" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD16" s="6" t="n"/>
+      <c r="BE16" s="6" t="n"/>
+      <c r="BF16" s="6" t="n"/>
+      <c r="BG16" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH16" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI16" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ16" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK16" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN16" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO16" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP16" s="7" t="n">
+        <v>46054</v>
+      </c>
+      <c r="BQ16" s="6" t="n"/>
+      <c r="BR16" s="6" t="n"/>
+      <c r="BS16" s="6" t="n"/>
+      <c r="BT16" s="6" t="n"/>
+      <c r="BU16" s="6" t="n"/>
+      <c r="BV16" s="6" t="n"/>
+      <c r="BW16" s="6" t="n"/>
+      <c r="BX16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
+      <c r="AB17" s="6" t="n"/>
+      <c r="AC17" s="6" t="n"/>
+      <c r="AD17" s="6" t="n"/>
+      <c r="AE17" s="6" t="n"/>
+      <c r="AF17" s="6" t="n"/>
+      <c r="AG17" s="6" t="n"/>
+      <c r="AH17" s="6" t="n"/>
+      <c r="AI17" s="6" t="n"/>
+      <c r="AJ17" s="6" t="n"/>
+      <c r="AK17" s="6" t="n"/>
+      <c r="AL17" s="6" t="n"/>
+      <c r="AM17" s="6" t="n"/>
+      <c r="AN17" s="6" t="n"/>
+      <c r="AO17" s="6" t="n"/>
+      <c r="AP17" s="6" t="n"/>
+      <c r="AQ17" s="6" t="n"/>
+      <c r="AR17" s="6" t="n"/>
+      <c r="AS17" s="6" t="n"/>
+      <c r="AT17" s="6" t="n"/>
+      <c r="AU17" s="6" t="n"/>
+      <c r="AV17" s="6" t="n"/>
+      <c r="AW17" s="6" t="n"/>
+      <c r="AX17" s="6" t="n"/>
+      <c r="AY17" s="6" t="n"/>
+      <c r="AZ17" s="6" t="n"/>
+      <c r="BA17" s="6" t="n"/>
+      <c r="BB17" s="6" t="n"/>
+      <c r="BC17" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD17" s="6" t="n"/>
+      <c r="BE17" s="6" t="n"/>
+      <c r="BF17" s="6" t="n"/>
+      <c r="BG17" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH17" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI17" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ17" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK17" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO17" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP17" s="7" t="n">
+        <v>46054</v>
+      </c>
+      <c r="BQ17" s="6" t="n"/>
+      <c r="BR17" s="6" t="n"/>
+      <c r="BS17" s="6" t="n"/>
+      <c r="BT17" s="6" t="n"/>
+      <c r="BU17" s="6" t="n"/>
+      <c r="BV17" s="6" t="n"/>
+      <c r="BW17" s="6" t="n"/>
+      <c r="BX17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>108</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>46058</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>16:53:44</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>46058</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>16:53:56</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>微信转账</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>维修</t>
+        </is>
+      </c>
+      <c r="AE18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>孟老师</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>13691204434</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>oHdTn5f_Pn7yTEDTHHJ0VqMP7zbM</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>微信转账</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>QJ_YH_260205_00001</t>
+        </is>
+      </c>
+      <c r="AP18" s="5" t="n">
+        <v>46058</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>16:53:44</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oHdTn5RBMZkgDb8KDc09Mbmm-j58</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>孟老师</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Fischer/费舍尔</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="BM18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP18" s="5" t="n">
+        <v>46059</v>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>微信转布乖 提现8997</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>46063</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>10:43:52</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="7" t="n">
+        <v>46063</v>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>10:43:58</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>修刃</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="n"/>
+      <c r="AE19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI19" s="6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ19" s="6" t="inlineStr">
+        <is>
+          <t>许</t>
+        </is>
+      </c>
+      <c r="AK19" s="6" t="inlineStr">
+        <is>
+          <t>19834679623</t>
+        </is>
+      </c>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5WLqRaAJfCVZgN7SKqHttoM</t>
+        </is>
+      </c>
+      <c r="AM19" s="6" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="AN19" s="6" t="n"/>
+      <c r="AO19" s="6" t="inlineStr">
+        <is>
+          <t>QJ_YH_260210_00001</t>
+        </is>
+      </c>
+      <c r="AP19" s="7" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AQ19" s="6" t="inlineStr">
+        <is>
+          <t>10:43:52</t>
+        </is>
+      </c>
+      <c r="AR19" s="6" t="n"/>
+      <c r="AS19" s="6" t="n"/>
+      <c r="AT19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5RBMZkgDb8KDc09Mbmm-j58</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="n"/>
+      <c r="AZ19" s="6" t="n"/>
+      <c r="BA19" s="6" t="inlineStr">
+        <is>
+          <t>许</t>
+        </is>
+      </c>
+      <c r="BB19" s="6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC19" s="6" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD19" s="6" t="inlineStr">
+        <is>
+          <t>Atomic/阿托米克</t>
+        </is>
+      </c>
+      <c r="BE19" s="6" t="n"/>
+      <c r="BF19" s="6" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="BG19" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH19" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI19" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ19" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK19" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP19" s="7" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BQ19" s="6" t="n"/>
+      <c r="BR19" s="6" t="n"/>
+      <c r="BS19" s="6" t="n"/>
+      <c r="BT19" s="6" t="n"/>
+      <c r="BU19" s="6" t="n"/>
+      <c r="BV19" s="6" t="n"/>
+      <c r="BW19" s="6" t="n"/>
+      <c r="BX19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+      <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
+      <c r="AA20" s="6" t="n"/>
+      <c r="AB20" s="6" t="n"/>
+      <c r="AC20" s="6" t="n"/>
+      <c r="AD20" s="6" t="n"/>
+      <c r="AE20" s="6" t="n"/>
+      <c r="AF20" s="6" t="n"/>
+      <c r="AG20" s="6" t="n"/>
+      <c r="AH20" s="6" t="n"/>
+      <c r="AI20" s="6" t="n"/>
+      <c r="AJ20" s="6" t="n"/>
+      <c r="AK20" s="6" t="n"/>
+      <c r="AL20" s="6" t="n"/>
+      <c r="AM20" s="6" t="n"/>
+      <c r="AN20" s="6" t="n"/>
+      <c r="AO20" s="6" t="n"/>
+      <c r="AP20" s="6" t="n"/>
+      <c r="AQ20" s="6" t="n"/>
+      <c r="AR20" s="6" t="n"/>
+      <c r="AS20" s="6" t="n"/>
+      <c r="AT20" s="6" t="n"/>
+      <c r="AU20" s="6" t="n"/>
+      <c r="AV20" s="6" t="n"/>
+      <c r="AW20" s="6" t="n"/>
+      <c r="AX20" s="6" t="n"/>
+      <c r="AY20" s="6" t="n"/>
+      <c r="AZ20" s="6" t="n"/>
+      <c r="BA20" s="6" t="n"/>
+      <c r="BB20" s="6" t="n"/>
+      <c r="BC20" s="6" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD20" s="6" t="inlineStr">
+        <is>
+          <t>Atomic/阿托米克</t>
+        </is>
+      </c>
+      <c r="BE20" s="6" t="n"/>
+      <c r="BF20" s="6" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="BG20" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH20" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI20" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ20" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK20" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP20" s="7" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="BR20" s="6" t="n"/>
+      <c r="BS20" s="6" t="n"/>
+      <c r="BT20" s="6" t="n"/>
+      <c r="BU20" s="6" t="n"/>
+      <c r="BV20" s="6" t="n"/>
+      <c r="BW20" s="6" t="n"/>
+      <c r="BX20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>46072</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>21:11:14</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="7" t="n">
+        <v>46072</v>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>21:11:40</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AD21" s="6" t="n"/>
+      <c r="AE21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI21" s="6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ21" s="6" t="inlineStr">
+        <is>
+          <t>张朴哲</t>
+        </is>
+      </c>
+      <c r="AK21" s="6" t="inlineStr">
+        <is>
+          <t>18519688902</t>
+        </is>
+      </c>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5VowdmC-9L3ViVagrUyOuTI</t>
+        </is>
+      </c>
+      <c r="AM21" s="6" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN21" s="6" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO21" s="6" t="inlineStr">
+        <is>
+          <t>QJ_YH_260219_00001</t>
+        </is>
+      </c>
+      <c r="AP21" s="7" t="n">
+        <v>46072</v>
+      </c>
+      <c r="AQ21" s="6" t="inlineStr">
+        <is>
+          <t>21:11:14</t>
+        </is>
+      </c>
+      <c r="AR21" s="6" t="n"/>
+      <c r="AS21" s="6" t="n"/>
+      <c r="AT21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AU21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AW21" s="6" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5f2n1MQfo1DsdN-azXHlajI</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="n"/>
+      <c r="AZ21" s="6" t="n"/>
+      <c r="BA21" s="6" t="inlineStr">
+        <is>
+          <t>张朴哲</t>
+        </is>
+      </c>
+      <c r="BB21" s="6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC21" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD21" s="6" t="inlineStr">
+        <is>
+          <t>新增品牌</t>
+        </is>
+      </c>
+      <c r="BE21" s="6" t="n"/>
+      <c r="BF21" s="6" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="BG21" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH21" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI21" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ21" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK21" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO21" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP21" s="7" t="n">
+        <v>46073</v>
+      </c>
+      <c r="BQ21" s="6" t="n"/>
+      <c r="BR21" s="6" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
+      <c r="BS21" s="6" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
+      <c r="BT21" s="6" t="n"/>
+      <c r="BU21" s="6" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
+      <c r="BV21" s="6" t="inlineStr">
+        <is>
+          <t>张凯</t>
+        </is>
+      </c>
+      <c r="BW21" s="6" t="n"/>
+      <c r="BX21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
+      <c r="AB22" s="6" t="n"/>
+      <c r="AC22" s="6" t="n"/>
+      <c r="AD22" s="6" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="6" t="n"/>
+      <c r="AG22" s="6" t="n"/>
+      <c r="AH22" s="6" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="6" t="n"/>
+      <c r="AK22" s="6" t="n"/>
+      <c r="AL22" s="6" t="n"/>
+      <c r="AM22" s="6" t="n"/>
+      <c r="AN22" s="6" t="n"/>
+      <c r="AO22" s="6" t="n"/>
+      <c r="AP22" s="6" t="n"/>
+      <c r="AQ22" s="6" t="n"/>
+      <c r="AR22" s="6" t="n"/>
+      <c r="AS22" s="6" t="n"/>
+      <c r="AT22" s="6" t="n"/>
+      <c r="AU22" s="6" t="n"/>
+      <c r="AV22" s="6" t="n"/>
+      <c r="AW22" s="6" t="n"/>
+      <c r="AX22" s="6" t="n"/>
+      <c r="AY22" s="6" t="n"/>
+      <c r="AZ22" s="6" t="n"/>
+      <c r="BA22" s="6" t="n"/>
+      <c r="BB22" s="6" t="n"/>
+      <c r="BC22" s="6" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD22" s="6" t="inlineStr">
+        <is>
+          <t>新增品牌</t>
+        </is>
+      </c>
+      <c r="BE22" s="6" t="n"/>
+      <c r="BF22" s="6" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="BG22" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH22" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI22" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ22" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK22" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO22" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP22" s="7" t="n">
+        <v>46073</v>
+      </c>
+      <c r="BQ22" s="6" t="n"/>
+      <c r="BR22" s="6" t="n"/>
+      <c r="BS22" s="6" t="n"/>
+      <c r="BT22" s="6" t="n"/>
+      <c r="BU22" s="6" t="n"/>
+      <c r="BV22" s="6" t="n"/>
+      <c r="BW22" s="6" t="n"/>
+      <c r="BX22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>126</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>46076</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>46076</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>19:45:43</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>13821265800</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>oHdTn5V5mJHwnzjw7IMyTIlHiJgw</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>QJ_YH_260223_00001</t>
+        </is>
+      </c>
+      <c r="AP23" s="5" t="n">
+        <v>46076</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>19:45:17</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>布乖（个人）</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>oHdTn5RBMZkgDb8KDc09Mbmm-j58</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>王</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP23" s="5" t="n">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>127</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>18:21:06</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡·维修</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>18801294821</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>oHdTn5d5NmN0a40mbK1B2tz0JM3c</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>QJ_YH_260224_00001</t>
+        </is>
+      </c>
+      <c r="AP24" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>18:21:06</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP24" s="5" t="n">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>127</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18:21:55</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>18:22:22</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡·维修</t>
+        </is>
+      </c>
+      <c r="AE25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>18801294821</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>oHdTn5d5NmN0a40mbK1B2tz0JM3c</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>QJ_YH_260224_00002</t>
+        </is>
+      </c>
+      <c r="AP25" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>18:21:55</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AU25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL25" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BM25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP25" s="5" t="n">
+        <v>46078</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>128</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>46078</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>19:06:44</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>46078</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>19:07:03</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>维修</t>
+        </is>
+      </c>
+      <c r="AE26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>18801294821</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>oHdTn5d5NmN0a40mbK1B2tz0JM3c</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>QJ_YH_260225_00001</t>
+        </is>
+      </c>
+      <c r="AP26" s="5" t="n">
+        <v>46078</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>19:06:44</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP26" s="5" t="n">
+        <v>46079</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>134</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12:54:20</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>12:55:35</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>修刃·维修</t>
+        </is>
+      </c>
+      <c r="AE27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>龚江</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>18257833218</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>oHdTn5Zfzy-2EOhnlWVv_2s1vRQk</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>QJ_YH_260303_00001</t>
+        </is>
+      </c>
+      <c r="AP27" s="5" t="n">
+        <v>46084</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>12:54:20</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="AU27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>龚江</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Head/海德</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BL27" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP27" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>配固定器中间连接片+螺丝 （50+50=100）
+重新安装竞技固定器（200）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>139</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>46089</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>17:07:05</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>46089</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>17:07:24</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>18801294821</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>oHdTn5d5NmN0a40mbK1B2tz0JM3c</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>QJ_YH_260308_00001</t>
+        </is>
+      </c>
+      <c r="AP28" s="5" t="n">
+        <v>46089</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>17:07:05</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN28" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP28" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="BX28" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>144</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>46094</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>19:18:41</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>46094</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>19:18:54</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>打蜡</t>
+        </is>
+      </c>
+      <c r="AE29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>18801294821</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>oHdTn5d5NmN0a40mbK1B2tz0JM3c</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>1636475482</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>QJ_YH_260313_00001</t>
+        </is>
+      </c>
+      <c r="AP29" s="5" t="n">
+        <v>46094</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>19:18:41</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AU29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>oHdTn5a0JEbKh7Rm31ilTEXGJ32Y</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>阿宝</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>单板</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Salomon/索罗门</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN29" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP29" s="5" t="n">
+        <v>46095</v>
+      </c>
+      <c r="BQ29" t="inlineStr">
+        <is>
+          <t>武士团特惠</t>
+        </is>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BU29" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+      <c r="BX29" t="inlineStr">
+        <is>
+          <t>崔洋（个人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>46104</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>13:36:29</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="7" t="n">
+        <v>46104</v>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>13:36:32</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="n"/>
+      <c r="W30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="Z30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="6" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AD30" s="6" t="n"/>
+      <c r="AE30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI30" s="6" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ30" s="6" t="inlineStr">
+        <is>
+          <t>胡东风</t>
+        </is>
+      </c>
+      <c r="AK30" s="6" t="inlineStr">
+        <is>
+          <t>13801076677</t>
+        </is>
+      </c>
+      <c r="AL30" s="6" t="n"/>
+      <c r="AM30" s="6" t="inlineStr">
+        <is>
+          <t>储值支付</t>
+        </is>
+      </c>
+      <c r="AN30" s="6" t="n"/>
+      <c r="AO30" s="6" t="inlineStr">
+        <is>
+          <t>QJ_YH_260323_00001</t>
+        </is>
+      </c>
+      <c r="AP30" s="7" t="n">
+        <v>46104</v>
+      </c>
+      <c r="AQ30" s="6" t="inlineStr">
+        <is>
+          <t>13:36:29</t>
+        </is>
+      </c>
+      <c r="AR30" s="6" t="n"/>
+      <c r="AS30" s="6" t="n"/>
+      <c r="AT30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="AU30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="AW30" s="6" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="n"/>
+      <c r="AZ30" s="6" t="n"/>
+      <c r="BA30" s="6" t="inlineStr">
+        <is>
+          <t>胡东风</t>
+        </is>
+      </c>
+      <c r="BB30" s="6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="BC30" s="6" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD30" s="6" t="inlineStr">
+        <is>
+          <t>Rossignol/金鸡</t>
+        </is>
+      </c>
+      <c r="BE30" s="6" t="n"/>
+      <c r="BF30" s="6" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="BG30" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH30" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI30" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ30" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK30" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP30" s="7" t="n">
+        <v>46105</v>
+      </c>
+      <c r="BQ30" s="6" t="n"/>
+      <c r="BR30" s="6" t="n"/>
+      <c r="BS30" s="6" t="n"/>
+      <c r="BT30" s="6" t="n"/>
+      <c r="BU30" s="6" t="n"/>
+      <c r="BV30" s="6" t="n"/>
+      <c r="BW30" s="6" t="n"/>
+      <c r="BX30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+      <c r="T31" s="6" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="6" t="n"/>
+      <c r="W31" s="6" t="n"/>
+      <c r="X31" s="6" t="n"/>
+      <c r="Y31" s="6" t="n"/>
+      <c r="Z31" s="6" t="n"/>
+      <c r="AA31" s="6" t="n"/>
+      <c r="AB31" s="6" t="n"/>
+      <c r="AC31" s="6" t="n"/>
+      <c r="AD31" s="6" t="n"/>
+      <c r="AE31" s="6" t="n"/>
+      <c r="AF31" s="6" t="n"/>
+      <c r="AG31" s="6" t="n"/>
+      <c r="AH31" s="6" t="n"/>
+      <c r="AI31" s="6" t="n"/>
+      <c r="AJ31" s="6" t="n"/>
+      <c r="AK31" s="6" t="n"/>
+      <c r="AL31" s="6" t="n"/>
+      <c r="AM31" s="6" t="n"/>
+      <c r="AN31" s="6" t="n"/>
+      <c r="AO31" s="6" t="n"/>
+      <c r="AP31" s="6" t="n"/>
+      <c r="AQ31" s="6" t="n"/>
+      <c r="AR31" s="6" t="n"/>
+      <c r="AS31" s="6" t="n"/>
+      <c r="AT31" s="6" t="n"/>
+      <c r="AU31" s="6" t="n"/>
+      <c r="AV31" s="6" t="n"/>
+      <c r="AW31" s="6" t="n"/>
+      <c r="AX31" s="6" t="n"/>
+      <c r="AY31" s="6" t="n"/>
+      <c r="AZ31" s="6" t="n"/>
+      <c r="BA31" s="6" t="n"/>
+      <c r="BB31" s="6" t="n"/>
+      <c r="BC31" s="6" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD31" s="6" t="inlineStr">
+        <is>
+          <t>Volkl/沃克</t>
+        </is>
+      </c>
+      <c r="BE31" s="6" t="n"/>
+      <c r="BF31" s="6" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="BG31" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BH31" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI31" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ31" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK31" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" s="8" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP31" s="7" t="n">
+        <v>46105</v>
+      </c>
+      <c r="BQ31" s="6" t="n"/>
+      <c r="BR31" s="6" t="n"/>
+      <c r="BS31" s="6" t="n"/>
+      <c r="BT31" s="6" t="n"/>
+      <c r="BU31" s="6" t="n"/>
+      <c r="BV31" s="6" t="n"/>
+      <c r="BW31" s="6" t="n"/>
+      <c r="BX31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>158</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>46108</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:44:05</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>修刃·打蜡·去蜡</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>养护</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>崇礼旗舰店</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>白雪景 (个人)</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>15810656580</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>oHdTn5cchichTZYYXEcs5oU8zlRI</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>QJ_YH_260327_00001</t>
+        </is>
+      </c>
+      <c r="AP32" s="5" t="n">
+        <v>46108</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>10:44:05</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oHdTn5aIENAKLpCCSxwMJWpX0JeQ</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>白雪景 (个人)</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>双板</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Adam/亚当</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BL32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BP32" s="5" t="n">
+        <v>46108</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="270">
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="AL11:AL12"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="AQ21:AQ22"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="AZ30:AZ31"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AK21:AK22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="AH19:AH20"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AN21:AN22"/>
+    <mergeCell ref="AT19:AT20"/>
+    <mergeCell ref="AV19:AV20"/>
+    <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="V30:V31"/>
+    <mergeCell ref="AG19:AG20"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="BB21:BB22"/>
+    <mergeCell ref="AY19:AY20"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="AP30:AP31"/>
+    <mergeCell ref="AH30:AH31"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="AS19:AS20"/>
+    <mergeCell ref="AJ30:AJ31"/>
+    <mergeCell ref="AR30:AR31"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AS16:AS17"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AP16:AP17"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AY16:AY17"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="AV16:AV17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="U30:U31"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="AV21:AV22"/>
+    <mergeCell ref="AE21:AE22"/>
+    <mergeCell ref="W30:W31"/>
+    <mergeCell ref="BA11:BA12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="AG21:AG22"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="AM19:AM20"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="AS21:AS22"/>
+    <mergeCell ref="O30:O31"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="AX11:AX12"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="AC30:AC31"/>
+    <mergeCell ref="AU30:AU31"/>
+    <mergeCell ref="AM30:AM31"/>
+    <mergeCell ref="AW30:AW31"/>
+    <mergeCell ref="AO30:AO31"/>
+    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AX16:AX17"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="AP19:AP20"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="AI16:AI17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AU16:AU17"/>
+    <mergeCell ref="AD30:AD31"/>
+    <mergeCell ref="AW16:AW17"/>
+    <mergeCell ref="AR16:AR17"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="AF30:AF31"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="AZ11:AZ12"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="BA16:BA17"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="AM21:AM22"/>
+    <mergeCell ref="N30:N31"/>
+    <mergeCell ref="AT30:AT31"/>
+    <mergeCell ref="AR11:AR12"/>
+    <mergeCell ref="P30:P31"/>
+    <mergeCell ref="AV30:AV31"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AX30:AX31"/>
+    <mergeCell ref="AF19:AF20"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="AX21:AX22"/>
+    <mergeCell ref="T30:T31"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="AP21:AP22"/>
+    <mergeCell ref="AO19:AO20"/>
+    <mergeCell ref="AH21:AH22"/>
+    <mergeCell ref="AO16:AO17"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="AL16:AL17"/>
+    <mergeCell ref="AU19:AU20"/>
+    <mergeCell ref="AN16:AN17"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="AZ16:AZ17"/>
+    <mergeCell ref="AR19:AR20"/>
+    <mergeCell ref="AI30:AI31"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="AK30:AK31"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="BA19:BA20"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="AN11:AN12"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="AB19:AB20"/>
+    <mergeCell ref="U21:U22"/>
+    <mergeCell ref="AR21:AR22"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="BA30:BA31"/>
+    <mergeCell ref="AY11:AY12"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="AO21:AO22"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="AA21:AA22"/>
+    <mergeCell ref="AQ30:AQ31"/>
+    <mergeCell ref="AH16:AH17"/>
+    <mergeCell ref="BB19:BB20"/>
+    <mergeCell ref="AU21:AU22"/>
+    <mergeCell ref="AS30:AS31"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="AT16:AT17"/>
+    <mergeCell ref="AL19:AL20"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="AX19:AX20"/>
+    <mergeCell ref="AZ19:AZ20"/>
+    <mergeCell ref="AQ16:AQ17"/>
+    <mergeCell ref="AI19:AI20"/>
+    <mergeCell ref="AY21:AY22"/>
+    <mergeCell ref="BB16:BB17"/>
+    <mergeCell ref="AK19:AK20"/>
+    <mergeCell ref="BA21:BA22"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="AB30:AB31"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="AL30:AL31"/>
+    <mergeCell ref="AW19:AW20"/>
+    <mergeCell ref="AN30:AN31"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="AB21:AB22"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AI11:AI12"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="BB30:BB31"/>
+    <mergeCell ref="AS11:AS12"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="AU11:AU12"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="AM11:AM12"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="AT21:AT22"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AL21:AL22"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="AF21:AF22"/>
+    <mergeCell ref="AK16:AK17"/>
+    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="AM16:AM17"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AZ21:AZ22"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="AQ19:AQ20"/>
+    <mergeCell ref="AJ16:AJ17"/>
+    <mergeCell ref="AW21:AW22"/>
+    <mergeCell ref="BB11:BB12"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="AN19:AN20"/>
+    <mergeCell ref="AE30:AE31"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AG30:AG31"/>
+    <mergeCell ref="AY30:AY31"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="L19:L20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>